--- a/Section2_Cleaned_Source.xlsx
+++ b/Section2_Cleaned_Source.xlsx
@@ -2,10 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleaned Section 2" sheetId="1" r:id="R70e39f6163444733"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Section 2 Summary" sheetId="2" r:id="R065c6bc2750d46c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Submission Coverage" sheetId="3" r:id="Rcccc116276f942b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" r:id="R2157f3cecb624235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleaned Section 2" sheetId="1" r:id="Rb7ba9fe8abaa4ed3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Section 2 Summary" sheetId="2" r:id="R6af35979168643fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Submission Coverage" sheetId="3" r:id="Rcd1b95f28af6438d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" r:id="R6d566aa65aa44086"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard Submission Roster" sheetId="5" r:id="Rc9197f1edc1d467a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -33,7 +34,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -60,6 +61,11 @@
         <x:fgColor rgb="FF113149"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF173F5D"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -68,7 +74,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -85,6 +91,8 @@
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -5790,4 +5798,347 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="17" t="str">
+        <x:v>Submission Ref</x:v>
+      </x:c>
+      <x:c r="B1" s="17" t="str">
+        <x:v>Faculty</x:v>
+      </x:c>
+      <x:c r="C1" s="17" t="str">
+        <x:v>Department</x:v>
+      </x:c>
+      <x:c r="D1" s="17" t="str">
+        <x:v>Session</x:v>
+      </x:c>
+      <x:c r="E1" s="17" t="str">
+        <x:v>Year</x:v>
+      </x:c>
+      <x:c r="F1" s="17" t="str">
+        <x:v>Retained Clean Entries</x:v>
+      </x:c>
+      <x:c r="G1" s="17" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>DELP58</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>Faculty of Social Sciences</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Department of Islamic Studies</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G2" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>DELP52</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Faculty of Social Sciences</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>School of Integrated Social Science</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G3" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>DELP51</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Faculty of Social Sciences</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>School of Integrated Social Science</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>DELP50</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Faculty of Information Technology</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Department of Computer Sciences &amp; IT</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F5" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G5" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>DELP44</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>University Institute of Diet &amp; Nutritional Sciences</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G6" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>DELP43</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Department of Health Professional Technologies</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G7" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>DELP41</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Faculty of Law</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>M.A Raoof College of Law</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>DELP39</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>University Institute of Diet &amp; Nutritional Sciences</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>DELP37</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Lahore School of Nursing</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F10" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>DELP36</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Faculty of Languages &amp; Literature</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Department of Urdu</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G11" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>DELP33</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Faculty of Information Technology</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Department of Software Engineering</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G12" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>DELP27</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Faculty of Social Sciences</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Department of Education</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F13" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G13" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>DELP21</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>Department of Optometry &amp; Vision Science</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Fall</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F14" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G14" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>DELP19</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Lahore Business School</x:v>
+      </x:c>
+      <x:c r="D15" t="str"/>
+      <x:c r="E15" t="str"/>
+      <x:c r="F15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Section 2 empty / placeholder only</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>DELP18</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>ERP</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>ERP</x:v>
+      </x:c>
+      <x:c r="D16" t="str"/>
+      <x:c r="E16" t="str"/>
+      <x:c r="F16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>Section 2 empty / placeholder only</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>